--- a/Project/Literature_Review.xlsx
+++ b/Project/Literature_Review.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\KLU\Y2--S1\ML\2520030605_ML_S4\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7313241E-A71D-4715-98F4-053E34C12FE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43C7DFE6-EEBA-4DFC-8A7F-6A9EE13280DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -499,7 +499,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
